--- a/docs/evidence/20261025_NonNV_AMD/NonNV_AMD.xlsx
+++ b/docs/evidence/20261025_NonNV_AMD/NonNV_AMD.xlsx
@@ -25935,7 +25935,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.90</t>
+      <t xml:space="preserve">0.91</t>
     </r>
     <r>
       <rPr>
@@ -26781,7 +26781,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1.07</t>
+      <t xml:space="preserve">1.12</t>
     </r>
     <r>
       <rPr>
@@ -26819,7 +26819,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1.40</t>
+      <t xml:space="preserve">1.35</t>
     </r>
     <r>
       <rPr>
@@ -26952,7 +26952,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.88</t>
+      <t xml:space="preserve">0.85</t>
     </r>
     <r>
       <rPr>
@@ -27001,7 +27001,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.88</t>
+      <t xml:space="preserve">0.85</t>
     </r>
     <r>
       <rPr>
